--- a/contest17_oubo.xlsx
+++ b/contest17_oubo.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1219A436-CAFF-45B8-85CE-682C1A7B4300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="応募用紙" sheetId="6" r:id="rId1"/>
@@ -19,96 +19,51 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">団体名簿!$A$1:$V$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'応募用紙'!A1:V70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'団体名簿'!A1:V74</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>応募用紙</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>年齢</t>
-    <rPh sb="0" eb="2">
-      <t>ネンレイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>住所</t>
-    <rPh sb="0" eb="2">
-      <t>ジュウショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>連絡先</t>
-    <rPh sb="0" eb="3">
-      <t>レンラクサキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>&lt;ふりがな&gt;</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>自由記入欄</t>
-    <rPh sb="0" eb="2">
-      <t>ジユウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キニュウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>〒</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　応募したコンテスト名：　　　　　　　　　　　　　　　　　　　　　　　　</t>
-    <rPh sb="1" eb="3">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>&lt;応募規約同意確認&gt;</t>
-    <rPh sb="1" eb="3">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>キヤク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ドウイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>）</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -116,9 +71,9 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -127,9 +82,9 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -137,9 +92,9 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -148,43 +103,21 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
       <t>または職業</t>
     </r>
-    <rPh sb="0" eb="2">
-      <t>ショゾク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ガッコウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ガクブ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ガッカ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ガクネン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ショクギョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -192,9 +125,9 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -203,178 +136,80 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
       <t>&lt;ゲームタイトル&gt;</t>
     </r>
-    <rPh sb="0" eb="2">
-      <t>サクヒン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>名</t>
-    <rPh sb="0" eb="1">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>&lt;制作期間&gt;</t>
-    <rPh sb="1" eb="3">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>キカン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>団体応募</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>―</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Tel</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Eメールアドレス</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>歳</t>
-    <rPh sb="0" eb="1">
-      <t>トシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　　　　　　　　　</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>万一、第三者の権利侵害に関わる問題が生じた場合は、すべて私が、私の責任と費用負担で解決するとともに、</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>第三者に生じた損害及び費用（弁護士費用を含む）を賠償します。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>月</t>
-    <rPh sb="0" eb="1">
-      <t>ツキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>私は、「福岡ゲームコンテスト」に関する広報・ＰＲのため、主催者及び主催者の認める第三者が、営利を目的とせず、</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>応募作品の試遊、公開、展示、印刷等（応募作品の画像等の提出を含む）を無償かつ無期限にて行うことができることに同意します。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>個人応募</t>
-    <rPh sb="0" eb="2">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>オウボ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>※記入された個人情報は厳重に取扱い、本事業の目的以外には使用いたしません。</t>
-    <rPh sb="1" eb="3">
-      <t>キニュウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ゲンジュウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>トリアツカ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ジギョウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>モクテキ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　　　　同意する方は✓をつけ、日付を記入してください。</t>
-    <rPh sb="4" eb="6">
-      <t>ドウイ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>キニュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>年</t>
-    <rPh sb="0" eb="1">
-      <t>ネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>日</t>
-    <rPh sb="0" eb="1">
-      <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>私は上記内容を理解し、承諾します。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>必ず連絡のとれる連絡先を</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>※</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>記入して下さい。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
@@ -383,39 +218,25 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
       <t>（団体の方は代表者氏名）</t>
     </r>
-    <rPh sb="5" eb="7">
-      <t>ダンタイ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ダイヒョウシャ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>どちらかに✓を
 つけてください。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -423,9 +244,9 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -434,30 +255,21 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
       <t>※他のコンテストへの
 応募をしている方のみ</t>
     </r>
-    <rPh sb="0" eb="1">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>オウボ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>応募した作品および作品を記録した媒体（ＤＶＤ、ＣＤ、USBメモリ）は、理由の如何を問わず、返却されないことに同意します。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>該当するものに✓をつけてください。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ゲームグラフィック・アート部門</t>
@@ -467,239 +279,99 @@
   </si>
   <si>
     <t>ゲームソフト部門    ※動作環境をご記入下さい</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>(</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ヶ月</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>団体名</t>
-    <rPh sb="0" eb="3">
-      <t>ダンタイメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>＜ふりがな＞</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>※団体応募の方は、メンバーの氏名を別紙名簿へご入力ください。</t>
-    <rPh sb="1" eb="3">
-      <t>ダンタイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ベッシ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>メイボ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>団体名簿</t>
-    <rPh sb="0" eb="4">
-      <t>ダンタイメイボ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>代表者</t>
-    <rPh sb="0" eb="3">
-      <t>ダイヒョウシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 1</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 2</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 3</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 4</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 5</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 6</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 7</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 8</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 9</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 10</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 11</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 12</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 13</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 14</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 15</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 16</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 17</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 18</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 19</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバー氏名 20</t>
-    <rPh sb="4" eb="6">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>学部・学科・専攻・学年 等</t>
   </si>
   <si>
-    <t>学部・学科・専攻・学年 等</t>
-    <rPh sb="0" eb="2">
-      <t>ガクブ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ガッカ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ガクネン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>トウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>第17回福岡ゲームコンテスト</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>GFF AWARD 2024</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ＡＩゲームグラフィック・アート部門</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　使用箇所 (例：初期のアイデア出し、敵キャラクター3体のキャラクターデザインの70％程度、プログラムの補助 等)</t>
@@ -711,9 +383,9 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
@@ -721,184 +393,87 @@
     </r>
     <r>
       <rPr>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
+        <color rgb="FF000000"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">
 ※200字以内</t>
     </r>
-    <rPh sb="54" eb="56">
-      <t>ブモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>私は、本作品が、第三者の著作権や名誉及びその他の権利を侵害しないものであることを保証します。また、 私は、AIツールの使用に</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>関して、現在の日本の法律で違反となるような行為や、既存の版権が問われるような作品の応募をしないことを保証します。</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　ＡＩツール名 (例：ChatGPT・Stable Diffusion 等)</t>
-    <rPh sb="6" eb="7">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>トウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　応募作品制作時にＡＩツールを使用した場合は下記をご記載ください。　</t>
-    <rPh sb="1" eb="5">
-      <t>オウボサクヒン</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>セイサクジ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>カキ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>キサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　※「ゲームグラフィック・アート部門」は、AIツールの使用を一切禁止しています。　​※「AIゲームグラフィック・アート部門」にご応募の方は、必ずこちらの欄に必要情報のご記入をお願い致します。​</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>菅 真栄</t>
-    <rPh sb="0" eb="1">
-      <t>スガ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>マエイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>すが まさえい</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>国際理工カレッジ ゲームクリエイター科 1年</t>
-    <rPh sb="0" eb="4">
-      <t>コクサイリコウ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>千葉県千葉市中央区都町7-9-20</t>
-    <rPh sb="0" eb="11">
-      <t>チバケンチバシチュウオウクミヤコチョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>260</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>0001</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>080-4476-1747</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>home.ei0408@gmail.com</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>POX</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ぽっくす</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>PC(Unity)</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>プログラムの学習, 検索に使用</t>
-    <rPh sb="6" eb="8">
-      <t>ガクシュウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>シンプルなUIや白黒カラーで制作するにあたってオリジナリティーを出すために、テーマにあった文字フォント自作しました。</t>
-    <rPh sb="8" eb="10">
-      <t>シロクロ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ジサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>BingAI(GPT4)</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ゲームクリエイター科 １年</t>
-    <rPh sb="9" eb="10">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ゲームクリエイター科 ２年</t>
-    <rPh sb="9" eb="10">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>POX制作チーム</t>
+  </si>
+  <si>
+    <t>ぽっくすせいさくちーむ</t>
+  </si>
+  <si>
+    <t>2024</t>
   </si>
 </sst>
 </file>
@@ -2704,38 +2279,24 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:ext cx="600075" cy="200025"/>
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4097" name="Check Box 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s4097"/>
-            </a:ext>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001100000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4097" name="Check Box 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="2447925" y="1600200"/>
+          <a:ext cx="600075" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2744,60 +2305,32 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p/>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:ext cx="447675" cy="447675"/>
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4098" name="Check Box 2" hidden="1">
-          <a:extLst>
-            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s4098"/>
-            </a:ext>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002100000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4098" name="Check Box 2" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="2447925" y="1905000"/>
+          <a:ext cx="447675" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2806,60 +2339,32 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p/>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>238125</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:ext cx="600075" cy="209550"/>
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4099" name="Check Box 3" hidden="1">
-          <a:extLst>
-            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s4099"/>
-            </a:ext>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003100000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4099" name="Check Box 3" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="47625" y="8658225"/>
+          <a:ext cx="600075" cy="209550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2868,60 +2373,32 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p/>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>9527</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:ext cx="342900" cy="400050"/>
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4100" name="Check Box 4" hidden="1">
-          <a:extLst>
-            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s4100"/>
-            </a:ext>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004100000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4100" name="Check Box 4" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="476250" y="22631400"/>
+          <a:ext cx="342900" cy="400050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2930,57 +2407,37 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p/>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>198783</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>99393</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>41412</xdr:colOff>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>132521</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="大かっこ 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="6" name="大かっこ 5"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4370733" y="1890093"/>
-          <a:ext cx="1195179" cy="490328"/>
+          <a:off x="4362450" y="1885950"/>
+          <a:ext cx="1200150" cy="495300"/>
         </a:xfrm>
         <a:prstGeom prst="bracketPair">
           <a:avLst/>
@@ -3016,37 +2473,23 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:ext cx="600075" cy="209550"/>
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4101" name="Check Box 5" hidden="1">
-          <a:extLst>
-            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s4101"/>
-            </a:ext>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005100000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4101" name="Check Box 5" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="38100" y="9277350"/>
+          <a:ext cx="600075" cy="209550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3055,60 +2498,32 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p/>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>276225</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:ext cx="600075" cy="209550"/>
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4102" name="Check Box 6" hidden="1">
-          <a:extLst>
-            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s4102"/>
-            </a:ext>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006100000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4102" name="Check Box 6" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="47625" y="9610725"/>
+          <a:ext cx="600075" cy="209550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3117,60 +2532,32 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p/>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:ext cx="600075" cy="209550"/>
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4104" name="Check Box 8" hidden="1">
-          <a:extLst>
-            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s4104"/>
-            </a:ext>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008100000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4104" name="Check Box 8" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="3505200" y="9277350"/>
+          <a:ext cx="600075" cy="209550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3179,498 +2566,15 @@
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p/>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2" name="Check Box 1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C05B3524-7AEA-C4B7-C7A1-79A622C7113B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>714375</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="Check Box 2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4098"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6A3F4B8-A88B-5C89-4B9B-84DF80ECEE55}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>47625</xdr:colOff>
-          <xdr:row>41</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>304800</xdr:colOff>
-          <xdr:row>41</xdr:row>
-          <xdr:rowOff>238125</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="Check Box 3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4099"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{448F57C5-D223-F95E-B1AF-9F541C8F15F1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="Check Box 4" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4100"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2374EA82-670E-C1DF-ADC6-43AE9BE810CB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>38100</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>295275</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>247650</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="Check Box 5" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4101"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8645917-EEC7-2B6C-C86A-1E64873C39F9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>47625</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>66675</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>304800</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>276225</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="Check Box 6" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4102"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95144C58-924A-3A8D-A4DE-521CD9096D8B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>295275</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>247650</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="Check Box 8" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4104"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CD52E56-7108-DB33-1C92-3905E698D8BD}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3965,7 +2869,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V80"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15" outlineLevelRow="0" defaultColWidth="9" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.75" style="1" customWidth="1"/>
@@ -3992,9 +2896,9 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="25.5" x14ac:dyDescent="0.15">
+    <row r="1" ht="25">
       <c r="A1" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4007,9 +2911,9 @@
       <c r="J1" s="57"/>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="1:22" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" customHeight="1" ht="56">
       <c r="A2" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4033,7 +2937,7 @@
       <c r="U2" s="62"/>
       <c r="V2" s="63"/>
     </row>
-    <row r="3" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" customHeight="1" ht="12">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -4055,7 +2959,7 @@
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
     </row>
-    <row r="4" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="14">
       <c r="N4" s="64" t="s">
         <v>26</v>
       </c>
@@ -4068,7 +2972,7 @@
       <c r="U4" s="64"/>
       <c r="V4" s="64"/>
     </row>
-    <row r="5" spans="1:22" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="5">
       <c r="A5" s="65" t="s">
         <v>35</v>
       </c>
@@ -4094,7 +2998,7 @@
       <c r="U5" s="2"/>
       <c r="V5" s="3"/>
     </row>
-    <row r="6" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" customHeight="1" ht="18">
       <c r="A6" s="68"/>
       <c r="B6" s="69"/>
       <c r="C6" s="69"/>
@@ -4113,7 +3017,9 @@
         <v>4</v>
       </c>
       <c r="N6" s="80"/>
-      <c r="O6" s="81"/>
+      <c r="O6" s="81" t="s">
+        <v>97</v>
+      </c>
       <c r="P6" s="81"/>
       <c r="Q6" s="81"/>
       <c r="R6" s="81"/>
@@ -4122,7 +3028,7 @@
       <c r="U6" s="81"/>
       <c r="V6" s="4"/>
     </row>
-    <row r="7" spans="1:22" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="7" ht="18">
       <c r="A7" s="68"/>
       <c r="B7" s="69"/>
       <c r="C7" s="69"/>
@@ -4141,7 +3047,9 @@
         <v>44</v>
       </c>
       <c r="N7" s="84"/>
-      <c r="O7" s="82"/>
+      <c r="O7" s="82" t="s">
+        <v>96</v>
+      </c>
       <c r="P7" s="82"/>
       <c r="Q7" s="82"/>
       <c r="R7" s="82"/>
@@ -4150,7 +3058,7 @@
       <c r="U7" s="82"/>
       <c r="V7" s="20"/>
     </row>
-    <row r="8" spans="1:22" ht="18.75" x14ac:dyDescent="0.15">
+    <row r="8" ht="18">
       <c r="A8" s="68"/>
       <c r="B8" s="69"/>
       <c r="C8" s="69"/>
@@ -4175,7 +3083,7 @@
       <c r="U8" s="83"/>
       <c r="V8" s="20"/>
     </row>
-    <row r="9" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" customHeight="1" ht="18">
       <c r="A9" s="71"/>
       <c r="B9" s="72"/>
       <c r="C9" s="72"/>
@@ -4203,7 +3111,7 @@
       <c r="U9" s="86"/>
       <c r="V9" s="54"/>
     </row>
-    <row r="10" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" ht="17">
       <c r="A10" s="107" t="s">
         <v>34</v>
       </c>
@@ -4215,7 +3123,7 @@
       </c>
       <c r="F10" s="121"/>
       <c r="G10" s="122" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H10" s="122"/>
       <c r="I10" s="122"/>
@@ -4237,13 +3145,13 @@
       <c r="U10" s="130"/>
       <c r="V10" s="25"/>
     </row>
-    <row r="11" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" customHeight="1" ht="11">
       <c r="A11" s="114"/>
       <c r="B11" s="115"/>
       <c r="C11" s="115"/>
       <c r="D11" s="116"/>
       <c r="E11" s="133" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11" s="134"/>
       <c r="G11" s="134"/>
@@ -4263,7 +3171,7 @@
       <c r="U11" s="131"/>
       <c r="V11" s="20"/>
     </row>
-    <row r="12" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12">
       <c r="A12" s="114"/>
       <c r="B12" s="115"/>
       <c r="C12" s="115"/>
@@ -4287,7 +3195,7 @@
       <c r="U12" s="131"/>
       <c r="V12" s="20"/>
     </row>
-    <row r="13" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" customHeight="1" ht="8">
       <c r="A13" s="114"/>
       <c r="B13" s="115"/>
       <c r="C13" s="115"/>
@@ -4311,7 +3219,7 @@
       <c r="U13" s="131"/>
       <c r="V13" s="26"/>
     </row>
-    <row r="14" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" customHeight="1" ht="12">
       <c r="A14" s="114"/>
       <c r="B14" s="115"/>
       <c r="C14" s="115"/>
@@ -4337,7 +3245,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="15" customHeight="1" ht="17">
       <c r="A15" s="117"/>
       <c r="B15" s="118"/>
       <c r="C15" s="118"/>
@@ -4361,7 +3269,7 @@
       <c r="U15" s="132"/>
       <c r="V15" s="88"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="16">
       <c r="A16" s="89" t="s">
         <v>10</v>
       </c>
@@ -4369,7 +3277,7 @@
       <c r="C16" s="90"/>
       <c r="D16" s="91"/>
       <c r="E16" s="98" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16" s="99"/>
       <c r="G16" s="99"/>
@@ -4389,7 +3297,7 @@
       <c r="U16" s="99"/>
       <c r="V16" s="100"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="17">
       <c r="A17" s="92"/>
       <c r="B17" s="93"/>
       <c r="C17" s="93"/>
@@ -4413,7 +3321,7 @@
       <c r="U17" s="102"/>
       <c r="V17" s="103"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="18">
       <c r="A18" s="92"/>
       <c r="B18" s="93"/>
       <c r="C18" s="93"/>
@@ -4437,7 +3345,7 @@
       <c r="U18" s="102"/>
       <c r="V18" s="103"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="19">
       <c r="A19" s="92"/>
       <c r="B19" s="93"/>
       <c r="C19" s="93"/>
@@ -4461,7 +3369,7 @@
       <c r="U19" s="102"/>
       <c r="V19" s="103"/>
     </row>
-    <row r="20" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="14">
       <c r="A20" s="95"/>
       <c r="B20" s="96"/>
       <c r="C20" s="96"/>
@@ -4485,7 +3393,7 @@
       <c r="U20" s="105"/>
       <c r="V20" s="106"/>
     </row>
-    <row r="21" spans="1:22" ht="18.75" x14ac:dyDescent="0.15">
+    <row r="21" ht="18">
       <c r="A21" s="107" t="s">
         <v>2</v>
       </c>
@@ -4496,14 +3404,14 @@
         <v>6</v>
       </c>
       <c r="F21" s="109" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G21" s="109"/>
       <c r="H21" s="28" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="110" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J21" s="110"/>
       <c r="K21" s="110"/>
@@ -4519,13 +3427,13 @@
       <c r="U21" s="110"/>
       <c r="V21" s="111"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="22">
       <c r="A22" s="92"/>
       <c r="B22" s="93"/>
       <c r="C22" s="93"/>
       <c r="D22" s="94"/>
       <c r="E22" s="101" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22" s="102"/>
       <c r="G22" s="102"/>
@@ -4545,7 +3453,7 @@
       <c r="U22" s="102"/>
       <c r="V22" s="103"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="23">
       <c r="A23" s="92"/>
       <c r="B23" s="93"/>
       <c r="C23" s="93"/>
@@ -4569,7 +3477,7 @@
       <c r="U23" s="102"/>
       <c r="V23" s="103"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="24">
       <c r="A24" s="92"/>
       <c r="B24" s="93"/>
       <c r="C24" s="93"/>
@@ -4593,7 +3501,7 @@
       <c r="U24" s="102"/>
       <c r="V24" s="103"/>
     </row>
-    <row r="25" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="14">
       <c r="A25" s="95"/>
       <c r="B25" s="96"/>
       <c r="C25" s="96"/>
@@ -4617,7 +3525,7 @@
       <c r="U25" s="105"/>
       <c r="V25" s="106"/>
     </row>
-    <row r="26" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" customHeight="1" ht="15">
       <c r="A26" s="107" t="s">
         <v>3</v>
       </c>
@@ -4629,7 +3537,7 @@
       </c>
       <c r="F26" s="146"/>
       <c r="G26" s="149" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H26" s="149"/>
       <c r="I26" s="149"/>
@@ -4647,7 +3555,7 @@
       <c r="U26" s="29"/>
       <c r="V26" s="25"/>
     </row>
-    <row r="27" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27">
       <c r="A27" s="92"/>
       <c r="B27" s="93"/>
       <c r="C27" s="93"/>
@@ -4668,7 +3576,7 @@
       <c r="R27" s="150"/>
       <c r="V27" s="20"/>
     </row>
-    <row r="28" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28">
       <c r="A28" s="92"/>
       <c r="B28" s="93"/>
       <c r="C28" s="93"/>
@@ -4696,7 +3604,7 @@
       <c r="U28" s="152"/>
       <c r="V28" s="31"/>
     </row>
-    <row r="29" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" customHeight="1" ht="18">
       <c r="A29" s="92"/>
       <c r="B29" s="93"/>
       <c r="C29" s="93"/>
@@ -4706,7 +3614,7 @@
       </c>
       <c r="F29" s="154"/>
       <c r="G29" s="157" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H29" s="157"/>
       <c r="I29" s="157"/>
@@ -4726,7 +3634,7 @@
       <c r="U29" s="152"/>
       <c r="V29" s="31"/>
     </row>
-    <row r="30" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30">
       <c r="A30" s="92"/>
       <c r="B30" s="93"/>
       <c r="C30" s="93"/>
@@ -4747,7 +3655,7 @@
       <c r="R30" s="150"/>
       <c r="V30" s="20"/>
     </row>
-    <row r="31" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="31" customHeight="1" ht="14">
       <c r="A31" s="142"/>
       <c r="B31" s="143"/>
       <c r="C31" s="143"/>
@@ -4771,8 +3679,8 @@
       <c r="U31" s="33"/>
       <c r="V31" s="34"/>
     </row>
-    <row r="32" spans="1:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:22" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="32" ht="15"/>
+    <row r="33" customHeight="1" ht="21">
       <c r="A33" s="159" t="s">
         <v>11</v>
       </c>
@@ -4783,7 +3691,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="168" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" s="168"/>
       <c r="H33" s="168"/>
@@ -4802,13 +3710,13 @@
       <c r="U33" s="168"/>
       <c r="V33" s="169"/>
     </row>
-    <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" customHeight="1" ht="15">
       <c r="A34" s="162"/>
       <c r="B34" s="163"/>
       <c r="C34" s="163"/>
       <c r="D34" s="164"/>
       <c r="E34" s="170" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F34" s="131"/>
       <c r="G34" s="131"/>
@@ -4828,7 +3736,7 @@
       <c r="U34" s="131"/>
       <c r="V34" s="171"/>
     </row>
-    <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" customHeight="1" ht="15">
       <c r="A35" s="162"/>
       <c r="B35" s="163"/>
       <c r="C35" s="163"/>
@@ -4852,7 +3760,7 @@
       <c r="U35" s="131"/>
       <c r="V35" s="171"/>
     </row>
-    <row r="36" spans="1:22" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="36" customHeight="1" ht="15">
       <c r="A36" s="162"/>
       <c r="B36" s="163"/>
       <c r="C36" s="163"/>
@@ -4876,7 +3784,7 @@
       <c r="U36" s="131"/>
       <c r="V36" s="171"/>
     </row>
-    <row r="37" spans="1:22" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="37" customHeight="1" ht="21">
       <c r="A37" s="165"/>
       <c r="B37" s="166"/>
       <c r="C37" s="166"/>
@@ -4906,7 +3814,7 @@
       </c>
       <c r="V37" s="176"/>
     </row>
-    <row r="38" spans="1:22" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="38" ht="17">
       <c r="A38" s="107" t="s">
         <v>36</v>
       </c>
@@ -4934,7 +3842,7 @@
       <c r="U38" s="197"/>
       <c r="V38" s="198"/>
     </row>
-    <row r="39" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39">
       <c r="A39" s="162"/>
       <c r="B39" s="163"/>
       <c r="C39" s="163"/>
@@ -4958,7 +3866,7 @@
       <c r="U39" s="137"/>
       <c r="V39" s="199"/>
     </row>
-    <row r="40" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="40" ht="14">
       <c r="A40" s="165"/>
       <c r="B40" s="166"/>
       <c r="C40" s="166"/>
@@ -4982,7 +3890,7 @@
       <c r="U40" s="140"/>
       <c r="V40" s="200"/>
     </row>
-    <row r="41" spans="1:22" ht="24" x14ac:dyDescent="0.15">
+    <row r="41" ht="24">
       <c r="A41" s="38" t="s">
         <v>38</v>
       </c>
@@ -5008,7 +3916,7 @@
       <c r="U41" s="40"/>
       <c r="V41" s="41"/>
     </row>
-    <row r="42" spans="1:22" ht="24" x14ac:dyDescent="0.15">
+    <row r="42" ht="24">
       <c r="A42" s="42"/>
       <c r="B42" s="43" t="s">
         <v>41</v>
@@ -5034,13 +3942,13 @@
       <c r="U42" s="40"/>
       <c r="V42" s="41"/>
     </row>
-    <row r="43" spans="1:22" ht="24" x14ac:dyDescent="0.15">
+    <row r="43" ht="24">
       <c r="A43" s="42"/>
       <c r="B43" s="44" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="137" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D43" s="137"/>
       <c r="E43" s="137"/>
@@ -5064,7 +3972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:22" ht="24" x14ac:dyDescent="0.15">
+    <row r="44" ht="24">
       <c r="A44" s="42"/>
       <c r="B44" s="43" t="s">
         <v>39</v>
@@ -5074,7 +3982,7 @@
       <c r="E44" s="45"/>
       <c r="F44" s="45"/>
       <c r="G44" s="43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H44" s="45"/>
       <c r="I44" s="45"/>
@@ -5092,7 +4000,7 @@
       <c r="U44" s="45"/>
       <c r="V44" s="6"/>
     </row>
-    <row r="45" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="45" ht="24">
       <c r="A45" s="42"/>
       <c r="B45" s="43" t="s">
         <v>40</v>
@@ -5118,7 +4026,7 @@
       <c r="U45" s="45"/>
       <c r="V45" s="6"/>
     </row>
-    <row r="46" spans="1:22" ht="75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" customHeight="1" ht="75">
       <c r="A46" s="201" t="s">
         <v>5</v>
       </c>
@@ -5126,7 +4034,7 @@
       <c r="C46" s="202"/>
       <c r="D46" s="202"/>
       <c r="E46" s="203" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F46" s="204"/>
       <c r="G46" s="204"/>
@@ -5146,9 +4054,9 @@
       <c r="U46" s="204"/>
       <c r="V46" s="205"/>
     </row>
-    <row r="47" spans="1:22" ht="75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" customHeight="1" ht="75">
       <c r="A47" s="177" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="178"/>
       <c r="C47" s="178"/>
@@ -5172,7 +4080,7 @@
       <c r="U47" s="178"/>
       <c r="V47" s="179"/>
     </row>
-    <row r="48" spans="1:22" ht="75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" customHeight="1" ht="75">
       <c r="A48" s="180"/>
       <c r="B48" s="181"/>
       <c r="C48" s="181"/>
@@ -5196,9 +4104,9 @@
       <c r="U48" s="181"/>
       <c r="V48" s="182"/>
     </row>
-    <row r="49" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" customHeight="1" ht="19">
       <c r="A49" s="193" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B49" s="194"/>
       <c r="C49" s="194"/>
@@ -5222,9 +4130,9 @@
       <c r="U49" s="194"/>
       <c r="V49" s="195"/>
     </row>
-    <row r="50" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" customHeight="1" ht="19">
       <c r="A50" s="183" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B50" s="184"/>
       <c r="C50" s="184"/>
@@ -5248,9 +4156,9 @@
       <c r="U50" s="184"/>
       <c r="V50" s="185"/>
     </row>
-    <row r="51" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" customHeight="1" ht="29">
       <c r="A51" s="190" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B51" s="191"/>
       <c r="C51" s="191"/>
@@ -5274,9 +4182,9 @@
       <c r="U51" s="191"/>
       <c r="V51" s="192"/>
     </row>
-    <row r="52" spans="1:22" s="55" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" customHeight="1" ht="150" customFormat="1" s="55">
       <c r="A52" s="209" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B52" s="210"/>
       <c r="C52" s="210"/>
@@ -5300,9 +4208,9 @@
       <c r="U52" s="210"/>
       <c r="V52" s="211"/>
     </row>
-    <row r="53" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" customHeight="1" ht="29">
       <c r="A53" s="190" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B53" s="191"/>
       <c r="C53" s="191"/>
@@ -5326,9 +4234,9 @@
       <c r="U53" s="191"/>
       <c r="V53" s="192"/>
     </row>
-    <row r="54" spans="1:22" ht="270" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="54" customHeight="1" ht="270">
       <c r="A54" s="186" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B54" s="187"/>
       <c r="C54" s="187"/>
@@ -5352,7 +4260,7 @@
       <c r="U54" s="187"/>
       <c r="V54" s="188"/>
     </row>
-    <row r="55" spans="1:22" ht="9" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="55" customHeight="1" ht="9">
       <c r="A55" s="56"/>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -5375,7 +4283,7 @@
       <c r="U55" s="13"/>
       <c r="V55" s="13"/>
     </row>
-    <row r="56" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" customHeight="1" ht="24">
       <c r="A56" s="214" t="s">
         <v>8</v>
       </c>
@@ -5401,7 +4309,7 @@
       <c r="U56" s="214"/>
       <c r="V56" s="214"/>
     </row>
-    <row r="57" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" customHeight="1" ht="14">
       <c r="A57" s="46"/>
       <c r="B57" s="46"/>
       <c r="C57" s="46"/>
@@ -5425,12 +4333,12 @@
       <c r="U57" s="46"/>
       <c r="V57" s="46"/>
     </row>
-    <row r="58" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" customHeight="1" ht="23">
       <c r="A58" s="47">
         <v>1</v>
       </c>
       <c r="B58" s="189" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58" s="189"/>
       <c r="D58" s="189"/>
@@ -5453,10 +4361,10 @@
       <c r="U58" s="189"/>
       <c r="V58" s="189"/>
     </row>
-    <row r="59" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" customHeight="1" ht="23">
       <c r="A59" s="47"/>
       <c r="B59" s="189" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C59" s="189"/>
       <c r="D59" s="189"/>
@@ -5479,7 +4387,7 @@
       <c r="U59" s="189"/>
       <c r="V59" s="189"/>
     </row>
-    <row r="60" spans="1:22" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" customHeight="1" ht="23" customFormat="1" s="19">
       <c r="A60" s="48"/>
       <c r="B60" s="189" t="s">
         <v>20</v>
@@ -5505,7 +4413,7 @@
       <c r="U60" s="189"/>
       <c r="V60" s="189"/>
     </row>
-    <row r="61" spans="1:22" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" customHeight="1" ht="23" customFormat="1" s="19">
       <c r="A61" s="48"/>
       <c r="B61" s="189" t="s">
         <v>21</v>
@@ -5531,7 +4439,7 @@
       <c r="U61" s="189"/>
       <c r="V61" s="189"/>
     </row>
-    <row r="62" spans="1:22" s="19" customFormat="1" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="62" ht="17" customFormat="1" s="19">
       <c r="A62" s="19" t="s">
         <v>19</v>
       </c>
@@ -5550,7 +4458,7 @@
       <c r="S62" s="49"/>
       <c r="T62" s="49"/>
     </row>
-    <row r="63" spans="1:22" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="63" ht="18" customFormat="1" s="19">
       <c r="A63" s="47">
         <v>2</v>
       </c>
@@ -5578,7 +4486,7 @@
       <c r="U63" s="189"/>
       <c r="V63" s="189"/>
     </row>
-    <row r="64" spans="1:22" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="64" ht="14">
       <c r="A64" s="32"/>
       <c r="B64" s="32"/>
       <c r="C64" s="32"/>
@@ -5602,7 +4510,7 @@
       <c r="U64" s="32"/>
       <c r="V64" s="32"/>
     </row>
-    <row r="65" spans="1:22" ht="18.75" x14ac:dyDescent="0.15">
+    <row r="65" ht="18">
       <c r="A65" s="39">
         <v>3</v>
       </c>
@@ -5630,7 +4538,7 @@
       <c r="U65" s="189"/>
       <c r="V65" s="189"/>
     </row>
-    <row r="66" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" customHeight="1" ht="23">
       <c r="A66" s="39"/>
       <c r="B66" s="189" t="s">
         <v>24</v>
@@ -5656,7 +4564,7 @@
       <c r="U66" s="189"/>
       <c r="V66" s="189"/>
     </row>
-    <row r="67" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" customHeight="1" ht="9">
       <c r="A67" s="207"/>
       <c r="B67" s="207"/>
       <c r="C67" s="207"/>
@@ -5680,7 +4588,7 @@
       <c r="U67" s="207"/>
       <c r="V67" s="207"/>
     </row>
-    <row r="68" spans="1:22" ht="18.75" x14ac:dyDescent="0.15">
+    <row r="68" ht="18">
       <c r="A68" s="189" t="s">
         <v>27</v>
       </c>
@@ -5706,8 +4614,8 @@
       <c r="U68" s="189"/>
       <c r="V68" s="189"/>
     </row>
-    <row r="69" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" spans="1:22" ht="21" x14ac:dyDescent="0.15">
+    <row r="69" customHeight="1" ht="6"/>
+    <row r="70" ht="21">
       <c r="B70" s="5"/>
       <c r="C70" s="21" t="s">
         <v>30</v>
@@ -5716,7 +4624,9 @@
       <c r="I70" s="21"/>
       <c r="J70" s="19"/>
       <c r="K70" s="19"/>
-      <c r="L70" s="208"/>
+      <c r="L70" s="208" t="s">
+        <v>98</v>
+      </c>
       <c r="M70" s="208"/>
       <c r="N70" s="39" t="s">
         <v>28</v>
@@ -5734,10 +4644,10 @@
       <c r="U70" s="19"/>
       <c r="V70" s="21"/>
     </row>
-    <row r="71" spans="1:22" ht="5.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" customHeight="1" ht="5">
       <c r="K71" s="1"/>
     </row>
-    <row r="72" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" customHeight="1" ht="27">
       <c r="A72" s="13"/>
       <c r="B72" s="13"/>
       <c r="C72" s="13"/>
@@ -5760,7 +4670,7 @@
       <c r="U72" s="13"/>
       <c r="V72" s="13"/>
     </row>
-    <row r="74" spans="1:22" ht="20.25" x14ac:dyDescent="0.15">
+    <row r="74" ht="20">
       <c r="A74" s="53"/>
       <c r="B74" s="212"/>
       <c r="C74" s="212"/>
@@ -5784,7 +4694,7 @@
       <c r="U74" s="212"/>
       <c r="V74" s="212"/>
     </row>
-    <row r="75" spans="1:22" ht="21" x14ac:dyDescent="0.15">
+    <row r="75" ht="21">
       <c r="B75" s="213"/>
       <c r="C75" s="213"/>
       <c r="D75" s="213"/>
@@ -5807,7 +4717,7 @@
       <c r="U75" s="213"/>
       <c r="V75" s="213"/>
     </row>
-    <row r="76" spans="1:22" s="19" customFormat="1" ht="21" x14ac:dyDescent="0.15">
+    <row r="76" ht="21" customFormat="1" s="19">
       <c r="B76" s="213"/>
       <c r="C76" s="213"/>
       <c r="D76" s="213"/>
@@ -5830,10 +4740,10 @@
       <c r="U76" s="213"/>
       <c r="V76" s="213"/>
     </row>
-    <row r="77" spans="1:22" s="19" customFormat="1" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="77" ht="17" customFormat="1" s="19">
       <c r="K77" s="43"/>
     </row>
-    <row r="78" spans="1:22" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.15">
+    <row r="78" ht="18" customFormat="1" s="19">
       <c r="A78" s="148"/>
       <c r="B78" s="148"/>
       <c r="C78" s="148"/>
@@ -5857,7 +4767,7 @@
       <c r="U78" s="148"/>
       <c r="V78" s="148"/>
     </row>
-    <row r="80" spans="1:22" ht="21" x14ac:dyDescent="0.15">
+    <row r="80" ht="21">
       <c r="H80" s="206"/>
       <c r="I80" s="206"/>
       <c r="J80" s="206"/>
@@ -5871,13 +4781,64 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="P15vh3BT/tI4LNKL+PZJyj2vmqPPMoZh+kReghbWuhmuNcQKB68+5J5PBJm9uIwqtREqQBVob/rpSqYk92uq7w==" saltValue="HOInmGsLr4hw33SvuOniPA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="70">
-    <mergeCell ref="B63:V63"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="A5:D9"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:J9"/>
+    <mergeCell ref="M7:N8"/>
+    <mergeCell ref="O7:U8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="A10:D15"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:Q10"/>
+    <mergeCell ref="R10:S15"/>
+    <mergeCell ref="T10:U15"/>
+    <mergeCell ref="E11:Q15"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="A16:D20"/>
+    <mergeCell ref="E16:V20"/>
+    <mergeCell ref="A21:D25"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="I21:V21"/>
+    <mergeCell ref="E22:V25"/>
+    <mergeCell ref="A26:D31"/>
+    <mergeCell ref="E26:F28"/>
+    <mergeCell ref="G26:R28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="E29:F31"/>
+    <mergeCell ref="G29:R31"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="A33:D37"/>
+    <mergeCell ref="F33:V33"/>
+    <mergeCell ref="E34:V36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:T37"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="A38:D40"/>
+    <mergeCell ref="H38:V38"/>
+    <mergeCell ref="E39:V40"/>
+    <mergeCell ref="C43:U43"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:V46"/>
+    <mergeCell ref="A47:V48"/>
+    <mergeCell ref="A49:V49"/>
+    <mergeCell ref="A50:V50"/>
+    <mergeCell ref="A51:V51"/>
+    <mergeCell ref="A52:V52"/>
+    <mergeCell ref="A53:V53"/>
+    <mergeCell ref="A54:V54"/>
     <mergeCell ref="A56:V56"/>
     <mergeCell ref="B58:V58"/>
+    <mergeCell ref="B59:V59"/>
     <mergeCell ref="B60:V60"/>
     <mergeCell ref="B61:V61"/>
-    <mergeCell ref="A78:V78"/>
-    <mergeCell ref="H80:P80"/>
+    <mergeCell ref="B63:V63"/>
     <mergeCell ref="B65:V65"/>
     <mergeCell ref="B66:V66"/>
     <mergeCell ref="A67:V67"/>
@@ -5888,59 +4849,8 @@
     <mergeCell ref="B74:V74"/>
     <mergeCell ref="B75:V75"/>
     <mergeCell ref="B76:V76"/>
-    <mergeCell ref="A38:D40"/>
-    <mergeCell ref="H38:V38"/>
-    <mergeCell ref="E39:V40"/>
-    <mergeCell ref="C43:U43"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:V46"/>
-    <mergeCell ref="A47:V48"/>
-    <mergeCell ref="A50:V50"/>
-    <mergeCell ref="A54:V54"/>
-    <mergeCell ref="B59:V59"/>
-    <mergeCell ref="A53:V53"/>
-    <mergeCell ref="A49:V49"/>
-    <mergeCell ref="A51:V51"/>
-    <mergeCell ref="A52:V52"/>
-    <mergeCell ref="A33:D37"/>
-    <mergeCell ref="F33:V33"/>
-    <mergeCell ref="E34:V36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:T37"/>
-    <mergeCell ref="U37:V37"/>
-    <mergeCell ref="A26:D31"/>
-    <mergeCell ref="E26:F28"/>
-    <mergeCell ref="G26:R28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="E29:F31"/>
-    <mergeCell ref="G29:R31"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="A16:D20"/>
-    <mergeCell ref="E16:V20"/>
-    <mergeCell ref="A21:D25"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I21:V21"/>
-    <mergeCell ref="E22:V25"/>
-    <mergeCell ref="A10:D15"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:Q10"/>
-    <mergeCell ref="R10:S15"/>
-    <mergeCell ref="T10:U15"/>
-    <mergeCell ref="E11:Q15"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="N4:V4"/>
-    <mergeCell ref="A5:D9"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:J9"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:U6"/>
-    <mergeCell ref="O7:U8"/>
-    <mergeCell ref="M7:N8"/>
-    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="A78:V78"/>
+    <mergeCell ref="H80:P80"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -6120,7 +5030,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V74"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15" outlineLevelRow="0" defaultColWidth="9" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.75" style="1" customWidth="1"/>
@@ -6147,9 +5057,9 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="25.5" x14ac:dyDescent="0.15">
+    <row r="1" ht="25">
       <c r="A1" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -6162,9 +5072,9 @@
       <c r="J1" s="57"/>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="1:22" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" customHeight="1" ht="56">
       <c r="A2" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -6188,7 +5098,7 @@
       <c r="U2" s="62"/>
       <c r="V2" s="63"/>
     </row>
-    <row r="3" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" customHeight="1" ht="12">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -6210,7 +5120,7 @@
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
     </row>
-    <row r="4" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="14">
       <c r="N4" s="64" t="s">
         <v>26</v>
       </c>
@@ -6223,7 +5133,7 @@
       <c r="U4" s="64"/>
       <c r="V4" s="64"/>
     </row>
-    <row r="5" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="5" customHeight="1" ht="18">
       <c r="A5" s="65" t="s">
         <v>44</v>
       </c>
@@ -6251,12 +5161,14 @@
       <c r="U5" s="217"/>
       <c r="V5" s="218"/>
     </row>
-    <row r="6" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" customHeight="1" ht="18">
       <c r="A6" s="68"/>
       <c r="B6" s="69"/>
       <c r="C6" s="69"/>
       <c r="D6" s="70"/>
-      <c r="E6" s="219"/>
+      <c r="E6" s="219" t="s">
+        <v>96</v>
+      </c>
       <c r="F6" s="220"/>
       <c r="G6" s="220"/>
       <c r="H6" s="220"/>
@@ -6275,7 +5187,7 @@
       <c r="U6" s="220"/>
       <c r="V6" s="221"/>
     </row>
-    <row r="7" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" customHeight="1" ht="17">
       <c r="A7" s="68"/>
       <c r="B7" s="69"/>
       <c r="C7" s="69"/>
@@ -6299,7 +5211,7 @@
       <c r="U7" s="223"/>
       <c r="V7" s="224"/>
     </row>
-    <row r="8" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" customHeight="1" ht="18">
       <c r="A8" s="68"/>
       <c r="B8" s="69"/>
       <c r="C8" s="69"/>
@@ -6323,7 +5235,7 @@
       <c r="U8" s="223"/>
       <c r="V8" s="224"/>
     </row>
-    <row r="9" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" customHeight="1" ht="18">
       <c r="A9" s="71"/>
       <c r="B9" s="72"/>
       <c r="C9" s="72"/>
@@ -6347,7 +5259,7 @@
       <c r="U9" s="226"/>
       <c r="V9" s="227"/>
     </row>
-    <row r="10" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" ht="18">
       <c r="A10" s="65" t="s">
         <v>48</v>
       </c>
@@ -6359,7 +5271,7 @@
       </c>
       <c r="F10" s="216"/>
       <c r="G10" s="217" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H10" s="217"/>
       <c r="I10" s="217"/>
@@ -6377,13 +5289,13 @@
       <c r="U10" s="217"/>
       <c r="V10" s="218"/>
     </row>
-    <row r="11" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" customHeight="1" ht="18">
       <c r="A11" s="68"/>
       <c r="B11" s="69"/>
       <c r="C11" s="69"/>
       <c r="D11" s="70"/>
       <c r="E11" s="219" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11" s="220"/>
       <c r="G11" s="220"/>
@@ -6403,7 +5315,7 @@
       <c r="U11" s="220"/>
       <c r="V11" s="221"/>
     </row>
-    <row r="12" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" customHeight="1" ht="17">
       <c r="A12" s="68"/>
       <c r="B12" s="69"/>
       <c r="C12" s="69"/>
@@ -6427,7 +5339,7 @@
       <c r="U12" s="223"/>
       <c r="V12" s="224"/>
     </row>
-    <row r="13" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" customHeight="1" ht="18">
       <c r="A13" s="68"/>
       <c r="B13" s="69"/>
       <c r="C13" s="69"/>
@@ -6451,7 +5363,7 @@
       <c r="U13" s="223"/>
       <c r="V13" s="224"/>
     </row>
-    <row r="14" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="14" customHeight="1" ht="18">
       <c r="A14" s="71"/>
       <c r="B14" s="72"/>
       <c r="C14" s="72"/>
@@ -6475,7 +5387,7 @@
       <c r="U14" s="226"/>
       <c r="V14" s="227"/>
     </row>
-    <row r="15" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="15" customHeight="1" ht="18">
       <c r="A15" s="65" t="s">
         <v>49</v>
       </c>
@@ -6494,20 +5406,20 @@
       <c r="L15" s="217"/>
       <c r="M15" s="228"/>
       <c r="N15" s="229" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O15" s="230"/>
       <c r="P15" s="230"/>
       <c r="Q15" s="231"/>
       <c r="R15" s="238" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S15" s="239"/>
       <c r="T15" s="239"/>
       <c r="U15" s="239"/>
       <c r="V15" s="240"/>
     </row>
-    <row r="16" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" customHeight="1" ht="18">
       <c r="A16" s="68"/>
       <c r="B16" s="69"/>
       <c r="C16" s="69"/>
@@ -6531,7 +5443,7 @@
       <c r="U16" s="242"/>
       <c r="V16" s="243"/>
     </row>
-    <row r="17" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="17" customHeight="1" ht="18">
       <c r="A17" s="71"/>
       <c r="B17" s="72"/>
       <c r="C17" s="72"/>
@@ -6555,7 +5467,7 @@
       <c r="U17" s="245"/>
       <c r="V17" s="246"/>
     </row>
-    <row r="18" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="18" customHeight="1" ht="18">
       <c r="A18" s="65" t="s">
         <v>50</v>
       </c>
@@ -6580,14 +5492,14 @@
       <c r="P18" s="230"/>
       <c r="Q18" s="231"/>
       <c r="R18" s="238" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S18" s="239"/>
       <c r="T18" s="239"/>
       <c r="U18" s="239"/>
       <c r="V18" s="240"/>
     </row>
-    <row r="19" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" customHeight="1" ht="18">
       <c r="A19" s="68"/>
       <c r="B19" s="69"/>
       <c r="C19" s="69"/>
@@ -6611,7 +5523,7 @@
       <c r="U19" s="242"/>
       <c r="V19" s="243"/>
     </row>
-    <row r="20" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="20" customHeight="1" ht="18">
       <c r="A20" s="71"/>
       <c r="B20" s="72"/>
       <c r="C20" s="72"/>
@@ -6635,7 +5547,7 @@
       <c r="U20" s="245"/>
       <c r="V20" s="246"/>
     </row>
-    <row r="21" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="21" customHeight="1" ht="18">
       <c r="A21" s="65" t="s">
         <v>51</v>
       </c>
@@ -6660,14 +5572,14 @@
       <c r="P21" s="230"/>
       <c r="Q21" s="231"/>
       <c r="R21" s="238" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S21" s="239"/>
       <c r="T21" s="239"/>
       <c r="U21" s="239"/>
       <c r="V21" s="240"/>
     </row>
-    <row r="22" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" customHeight="1" ht="18">
       <c r="A22" s="249"/>
       <c r="B22" s="233"/>
       <c r="C22" s="233"/>
@@ -6691,7 +5603,7 @@
       <c r="U22" s="242"/>
       <c r="V22" s="243"/>
     </row>
-    <row r="23" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="23" customHeight="1" ht="18">
       <c r="A23" s="250"/>
       <c r="B23" s="251"/>
       <c r="C23" s="251"/>
@@ -6715,7 +5627,7 @@
       <c r="U23" s="245"/>
       <c r="V23" s="246"/>
     </row>
-    <row r="24" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="24" customHeight="1" ht="18">
       <c r="A24" s="65" t="s">
         <v>52</v>
       </c>
@@ -6740,14 +5652,14 @@
       <c r="P24" s="230"/>
       <c r="Q24" s="231"/>
       <c r="R24" s="238" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S24" s="239"/>
       <c r="T24" s="239"/>
       <c r="U24" s="239"/>
       <c r="V24" s="240"/>
     </row>
-    <row r="25" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" customHeight="1" ht="18">
       <c r="A25" s="249"/>
       <c r="B25" s="233"/>
       <c r="C25" s="233"/>
@@ -6771,7 +5683,7 @@
       <c r="U25" s="242"/>
       <c r="V25" s="243"/>
     </row>
-    <row r="26" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="26" customHeight="1" ht="18">
       <c r="A26" s="250"/>
       <c r="B26" s="251"/>
       <c r="C26" s="251"/>
@@ -6795,7 +5707,7 @@
       <c r="U26" s="245"/>
       <c r="V26" s="246"/>
     </row>
-    <row r="27" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="27" customHeight="1" ht="18">
       <c r="A27" s="65" t="s">
         <v>53</v>
       </c>
@@ -6820,14 +5732,14 @@
       <c r="P27" s="230"/>
       <c r="Q27" s="231"/>
       <c r="R27" s="238" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S27" s="239"/>
       <c r="T27" s="239"/>
       <c r="U27" s="239"/>
       <c r="V27" s="240"/>
     </row>
-    <row r="28" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" customHeight="1" ht="18">
       <c r="A28" s="249"/>
       <c r="B28" s="233"/>
       <c r="C28" s="233"/>
@@ -6851,7 +5763,7 @@
       <c r="U28" s="242"/>
       <c r="V28" s="243"/>
     </row>
-    <row r="29" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="29" customHeight="1" ht="18">
       <c r="A29" s="250"/>
       <c r="B29" s="251"/>
       <c r="C29" s="251"/>
@@ -6875,7 +5787,7 @@
       <c r="U29" s="245"/>
       <c r="V29" s="246"/>
     </row>
-    <row r="30" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="30" customHeight="1" ht="18">
       <c r="A30" s="65" t="s">
         <v>54</v>
       </c>
@@ -6900,14 +5812,14 @@
       <c r="P30" s="230"/>
       <c r="Q30" s="231"/>
       <c r="R30" s="238" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S30" s="239"/>
       <c r="T30" s="239"/>
       <c r="U30" s="239"/>
       <c r="V30" s="240"/>
     </row>
-    <row r="31" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" customHeight="1" ht="18">
       <c r="A31" s="249"/>
       <c r="B31" s="233"/>
       <c r="C31" s="233"/>
@@ -6931,7 +5843,7 @@
       <c r="U31" s="242"/>
       <c r="V31" s="243"/>
     </row>
-    <row r="32" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="32" customHeight="1" ht="18">
       <c r="A32" s="250"/>
       <c r="B32" s="251"/>
       <c r="C32" s="251"/>
@@ -6955,7 +5867,7 @@
       <c r="U32" s="245"/>
       <c r="V32" s="246"/>
     </row>
-    <row r="33" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="33" customHeight="1" ht="18">
       <c r="A33" s="65" t="s">
         <v>55</v>
       </c>
@@ -6980,14 +5892,14 @@
       <c r="P33" s="230"/>
       <c r="Q33" s="231"/>
       <c r="R33" s="238" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S33" s="239"/>
       <c r="T33" s="239"/>
       <c r="U33" s="239"/>
       <c r="V33" s="240"/>
     </row>
-    <row r="34" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" customHeight="1" ht="18">
       <c r="A34" s="249"/>
       <c r="B34" s="233"/>
       <c r="C34" s="233"/>
@@ -7011,7 +5923,7 @@
       <c r="U34" s="242"/>
       <c r="V34" s="243"/>
     </row>
-    <row r="35" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="35" customHeight="1" ht="18">
       <c r="A35" s="250"/>
       <c r="B35" s="251"/>
       <c r="C35" s="251"/>
@@ -7035,7 +5947,7 @@
       <c r="U35" s="245"/>
       <c r="V35" s="246"/>
     </row>
-    <row r="36" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="36" customHeight="1" ht="18">
       <c r="A36" s="65" t="s">
         <v>56</v>
       </c>
@@ -7065,7 +5977,7 @@
       <c r="U36" s="239"/>
       <c r="V36" s="240"/>
     </row>
-    <row r="37" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" customHeight="1" ht="18">
       <c r="A37" s="249"/>
       <c r="B37" s="233"/>
       <c r="C37" s="233"/>
@@ -7089,7 +6001,7 @@
       <c r="U37" s="242"/>
       <c r="V37" s="243"/>
     </row>
-    <row r="38" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="38" customHeight="1" ht="18">
       <c r="A38" s="250"/>
       <c r="B38" s="251"/>
       <c r="C38" s="251"/>
@@ -7113,7 +6025,7 @@
       <c r="U38" s="245"/>
       <c r="V38" s="246"/>
     </row>
-    <row r="39" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="39" customHeight="1" ht="18">
       <c r="A39" s="65" t="s">
         <v>57</v>
       </c>
@@ -7143,7 +6055,7 @@
       <c r="U39" s="239"/>
       <c r="V39" s="240"/>
     </row>
-    <row r="40" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" customHeight="1" ht="18">
       <c r="A40" s="249"/>
       <c r="B40" s="233"/>
       <c r="C40" s="233"/>
@@ -7167,7 +6079,7 @@
       <c r="U40" s="242"/>
       <c r="V40" s="243"/>
     </row>
-    <row r="41" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="41" customHeight="1" ht="18">
       <c r="A41" s="250"/>
       <c r="B41" s="251"/>
       <c r="C41" s="251"/>
@@ -7191,7 +6103,7 @@
       <c r="U41" s="245"/>
       <c r="V41" s="246"/>
     </row>
-    <row r="42" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="42" customHeight="1" ht="18">
       <c r="A42" s="65" t="s">
         <v>58</v>
       </c>
@@ -7221,7 +6133,7 @@
       <c r="U42" s="239"/>
       <c r="V42" s="240"/>
     </row>
-    <row r="43" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" customHeight="1" ht="18">
       <c r="A43" s="249"/>
       <c r="B43" s="233"/>
       <c r="C43" s="233"/>
@@ -7245,7 +6157,7 @@
       <c r="U43" s="242"/>
       <c r="V43" s="243"/>
     </row>
-    <row r="44" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="44" customHeight="1" ht="18">
       <c r="A44" s="250"/>
       <c r="B44" s="251"/>
       <c r="C44" s="251"/>
@@ -7269,7 +6181,7 @@
       <c r="U44" s="245"/>
       <c r="V44" s="246"/>
     </row>
-    <row r="45" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="45" customHeight="1" ht="18">
       <c r="A45" s="65" t="s">
         <v>59</v>
       </c>
@@ -7299,7 +6211,7 @@
       <c r="U45" s="239"/>
       <c r="V45" s="240"/>
     </row>
-    <row r="46" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" customHeight="1" ht="18">
       <c r="A46" s="249"/>
       <c r="B46" s="233"/>
       <c r="C46" s="233"/>
@@ -7323,7 +6235,7 @@
       <c r="U46" s="242"/>
       <c r="V46" s="243"/>
     </row>
-    <row r="47" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="47" customHeight="1" ht="18">
       <c r="A47" s="250"/>
       <c r="B47" s="251"/>
       <c r="C47" s="251"/>
@@ -7347,7 +6259,7 @@
       <c r="U47" s="245"/>
       <c r="V47" s="246"/>
     </row>
-    <row r="48" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="48" customHeight="1" ht="18">
       <c r="A48" s="65" t="s">
         <v>60</v>
       </c>
@@ -7377,7 +6289,7 @@
       <c r="U48" s="239"/>
       <c r="V48" s="240"/>
     </row>
-    <row r="49" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" customHeight="1" ht="18">
       <c r="A49" s="249"/>
       <c r="B49" s="233"/>
       <c r="C49" s="233"/>
@@ -7401,7 +6313,7 @@
       <c r="U49" s="242"/>
       <c r="V49" s="243"/>
     </row>
-    <row r="50" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="50" customHeight="1" ht="18">
       <c r="A50" s="250"/>
       <c r="B50" s="251"/>
       <c r="C50" s="251"/>
@@ -7425,7 +6337,7 @@
       <c r="U50" s="245"/>
       <c r="V50" s="246"/>
     </row>
-    <row r="51" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="51" customHeight="1" ht="18">
       <c r="A51" s="65" t="s">
         <v>61</v>
       </c>
@@ -7455,7 +6367,7 @@
       <c r="U51" s="239"/>
       <c r="V51" s="240"/>
     </row>
-    <row r="52" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" customHeight="1" ht="18">
       <c r="A52" s="249"/>
       <c r="B52" s="233"/>
       <c r="C52" s="233"/>
@@ -7479,7 +6391,7 @@
       <c r="U52" s="242"/>
       <c r="V52" s="243"/>
     </row>
-    <row r="53" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="53" customHeight="1" ht="18">
       <c r="A53" s="250"/>
       <c r="B53" s="251"/>
       <c r="C53" s="251"/>
@@ -7503,7 +6415,7 @@
       <c r="U53" s="245"/>
       <c r="V53" s="246"/>
     </row>
-    <row r="54" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="54" customHeight="1" ht="18">
       <c r="A54" s="65" t="s">
         <v>62</v>
       </c>
@@ -7533,7 +6445,7 @@
       <c r="U54" s="239"/>
       <c r="V54" s="240"/>
     </row>
-    <row r="55" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" customHeight="1" ht="18">
       <c r="A55" s="249"/>
       <c r="B55" s="233"/>
       <c r="C55" s="233"/>
@@ -7557,7 +6469,7 @@
       <c r="U55" s="242"/>
       <c r="V55" s="243"/>
     </row>
-    <row r="56" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="56" customHeight="1" ht="18">
       <c r="A56" s="250"/>
       <c r="B56" s="251"/>
       <c r="C56" s="251"/>
@@ -7581,7 +6493,7 @@
       <c r="U56" s="245"/>
       <c r="V56" s="246"/>
     </row>
-    <row r="57" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="57" customHeight="1" ht="18">
       <c r="A57" s="65" t="s">
         <v>63</v>
       </c>
@@ -7611,7 +6523,7 @@
       <c r="U57" s="239"/>
       <c r="V57" s="240"/>
     </row>
-    <row r="58" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" customHeight="1" ht="18">
       <c r="A58" s="249"/>
       <c r="B58" s="233"/>
       <c r="C58" s="233"/>
@@ -7635,7 +6547,7 @@
       <c r="U58" s="242"/>
       <c r="V58" s="243"/>
     </row>
-    <row r="59" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="59" customHeight="1" ht="18">
       <c r="A59" s="250"/>
       <c r="B59" s="251"/>
       <c r="C59" s="251"/>
@@ -7659,7 +6571,7 @@
       <c r="U59" s="245"/>
       <c r="V59" s="246"/>
     </row>
-    <row r="60" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="60" customHeight="1" ht="18">
       <c r="A60" s="65" t="s">
         <v>64</v>
       </c>
@@ -7689,7 +6601,7 @@
       <c r="U60" s="239"/>
       <c r="V60" s="240"/>
     </row>
-    <row r="61" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" customHeight="1" ht="18">
       <c r="A61" s="249"/>
       <c r="B61" s="233"/>
       <c r="C61" s="233"/>
@@ -7713,7 +6625,7 @@
       <c r="U61" s="242"/>
       <c r="V61" s="243"/>
     </row>
-    <row r="62" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="62" customHeight="1" ht="18">
       <c r="A62" s="250"/>
       <c r="B62" s="251"/>
       <c r="C62" s="251"/>
@@ -7737,7 +6649,7 @@
       <c r="U62" s="245"/>
       <c r="V62" s="246"/>
     </row>
-    <row r="63" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="63" customHeight="1" ht="18">
       <c r="A63" s="65" t="s">
         <v>65</v>
       </c>
@@ -7767,7 +6679,7 @@
       <c r="U63" s="239"/>
       <c r="V63" s="240"/>
     </row>
-    <row r="64" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" customHeight="1" ht="18">
       <c r="A64" s="249"/>
       <c r="B64" s="233"/>
       <c r="C64" s="233"/>
@@ -7791,7 +6703,7 @@
       <c r="U64" s="242"/>
       <c r="V64" s="243"/>
     </row>
-    <row r="65" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="65" customHeight="1" ht="18">
       <c r="A65" s="250"/>
       <c r="B65" s="251"/>
       <c r="C65" s="251"/>
@@ -7815,7 +6727,7 @@
       <c r="U65" s="245"/>
       <c r="V65" s="246"/>
     </row>
-    <row r="66" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="66" customHeight="1" ht="18">
       <c r="A66" s="65" t="s">
         <v>66</v>
       </c>
@@ -7845,7 +6757,7 @@
       <c r="U66" s="239"/>
       <c r="V66" s="240"/>
     </row>
-    <row r="67" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" customHeight="1" ht="18">
       <c r="A67" s="249"/>
       <c r="B67" s="233"/>
       <c r="C67" s="233"/>
@@ -7869,7 +6781,7 @@
       <c r="U67" s="242"/>
       <c r="V67" s="243"/>
     </row>
-    <row r="68" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="68" customHeight="1" ht="18">
       <c r="A68" s="250"/>
       <c r="B68" s="251"/>
       <c r="C68" s="251"/>
@@ -7893,7 +6805,7 @@
       <c r="U68" s="245"/>
       <c r="V68" s="246"/>
     </row>
-    <row r="69" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="69" customHeight="1" ht="18">
       <c r="A69" s="65" t="s">
         <v>67</v>
       </c>
@@ -7923,7 +6835,7 @@
       <c r="U69" s="239"/>
       <c r="V69" s="240"/>
     </row>
-    <row r="70" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" customHeight="1" ht="18">
       <c r="A70" s="249"/>
       <c r="B70" s="233"/>
       <c r="C70" s="233"/>
@@ -7947,7 +6859,7 @@
       <c r="U70" s="242"/>
       <c r="V70" s="243"/>
     </row>
-    <row r="71" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="71" customHeight="1" ht="18">
       <c r="A71" s="250"/>
       <c r="B71" s="251"/>
       <c r="C71" s="251"/>
@@ -7971,7 +6883,7 @@
       <c r="U71" s="245"/>
       <c r="V71" s="246"/>
     </row>
-    <row r="72" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="72" customHeight="1" ht="18">
       <c r="A72" s="65" t="s">
         <v>68</v>
       </c>
@@ -8001,7 +6913,7 @@
       <c r="U72" s="239"/>
       <c r="V72" s="240"/>
     </row>
-    <row r="73" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" customHeight="1" ht="18">
       <c r="A73" s="249"/>
       <c r="B73" s="233"/>
       <c r="C73" s="233"/>
@@ -8025,7 +6937,7 @@
       <c r="U73" s="242"/>
       <c r="V73" s="243"/>
     </row>
-    <row r="74" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="74" customHeight="1" ht="18">
       <c r="A74" s="253"/>
       <c r="B74" s="236"/>
       <c r="C74" s="236"/>
@@ -8052,82 +6964,57 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Nc05L7HJGOvEGYoSyzOY3XX1YrHCLjTjs9GIRIq8AhA3p4HLeESXIUhU2wdB8QVddga82Uh0z+CtKFDpF5I1+Q==" saltValue="+0GKbRNY8cuFZEZODnxJgw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="132">
-    <mergeCell ref="A57:D59"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:M57"/>
-    <mergeCell ref="N57:Q59"/>
-    <mergeCell ref="R57:V59"/>
-    <mergeCell ref="E58:M59"/>
-    <mergeCell ref="A66:D68"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="G66:M66"/>
-    <mergeCell ref="N66:Q68"/>
-    <mergeCell ref="R66:V68"/>
-    <mergeCell ref="E67:M68"/>
-    <mergeCell ref="A63:D65"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G63:M63"/>
-    <mergeCell ref="N63:Q65"/>
-    <mergeCell ref="R63:V65"/>
-    <mergeCell ref="E64:M65"/>
-    <mergeCell ref="A54:D56"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G54:M54"/>
-    <mergeCell ref="N54:Q56"/>
-    <mergeCell ref="R54:V56"/>
-    <mergeCell ref="E55:M56"/>
-    <mergeCell ref="A72:D74"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G72:M72"/>
-    <mergeCell ref="N72:Q74"/>
-    <mergeCell ref="R72:V74"/>
-    <mergeCell ref="E73:M74"/>
-    <mergeCell ref="A69:D71"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="G69:M69"/>
-    <mergeCell ref="N69:Q71"/>
-    <mergeCell ref="R69:V71"/>
-    <mergeCell ref="E70:M71"/>
-    <mergeCell ref="A60:D62"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G60:M60"/>
-    <mergeCell ref="N60:Q62"/>
-    <mergeCell ref="R60:V62"/>
-    <mergeCell ref="E61:M62"/>
-    <mergeCell ref="A51:D53"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="G51:M51"/>
-    <mergeCell ref="N51:Q53"/>
-    <mergeCell ref="R51:V53"/>
-    <mergeCell ref="E52:M53"/>
-    <mergeCell ref="A48:D50"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="G48:M48"/>
-    <mergeCell ref="N48:Q50"/>
-    <mergeCell ref="R48:V50"/>
-    <mergeCell ref="E49:M50"/>
-    <mergeCell ref="A45:D47"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="G45:M45"/>
-    <mergeCell ref="N45:Q47"/>
-    <mergeCell ref="R45:V47"/>
-    <mergeCell ref="E46:M47"/>
-    <mergeCell ref="R39:V41"/>
-    <mergeCell ref="E40:M41"/>
-    <mergeCell ref="A42:D44"/>
-    <mergeCell ref="G42:M42"/>
-    <mergeCell ref="N42:Q44"/>
-    <mergeCell ref="R42:V44"/>
-    <mergeCell ref="E43:M44"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="A39:D41"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:M39"/>
-    <mergeCell ref="N39:Q41"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="A5:D9"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:V5"/>
+    <mergeCell ref="E6:V9"/>
+    <mergeCell ref="A10:D14"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:V10"/>
+    <mergeCell ref="E11:V14"/>
+    <mergeCell ref="A15:D17"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:M15"/>
+    <mergeCell ref="N15:Q17"/>
+    <mergeCell ref="R15:V17"/>
+    <mergeCell ref="E16:M17"/>
+    <mergeCell ref="A18:D20"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:M18"/>
+    <mergeCell ref="N18:Q20"/>
+    <mergeCell ref="R18:V20"/>
+    <mergeCell ref="E19:M20"/>
+    <mergeCell ref="A21:D23"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:M21"/>
+    <mergeCell ref="N21:Q23"/>
+    <mergeCell ref="R21:V23"/>
+    <mergeCell ref="E22:M23"/>
+    <mergeCell ref="A24:D26"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:M24"/>
+    <mergeCell ref="N24:Q26"/>
+    <mergeCell ref="R24:V26"/>
+    <mergeCell ref="E25:M26"/>
+    <mergeCell ref="A27:D29"/>
+    <mergeCell ref="E27:F27"/>
     <mergeCell ref="G27:M27"/>
     <mergeCell ref="N27:Q29"/>
     <mergeCell ref="R27:V29"/>
     <mergeCell ref="E28:M29"/>
+    <mergeCell ref="A30:D32"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:M30"/>
+    <mergeCell ref="N30:Q32"/>
+    <mergeCell ref="R30:V32"/>
+    <mergeCell ref="E31:M32"/>
+    <mergeCell ref="A33:D35"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:M33"/>
     <mergeCell ref="N33:Q35"/>
     <mergeCell ref="R33:V35"/>
     <mergeCell ref="E34:M35"/>
@@ -8137,53 +7024,78 @@
     <mergeCell ref="N36:Q38"/>
     <mergeCell ref="R36:V38"/>
     <mergeCell ref="E37:M38"/>
-    <mergeCell ref="A33:D35"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:M33"/>
-    <mergeCell ref="A21:D23"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="R15:V17"/>
-    <mergeCell ref="G21:M21"/>
-    <mergeCell ref="N21:Q23"/>
-    <mergeCell ref="R21:V23"/>
-    <mergeCell ref="A30:D32"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:M30"/>
-    <mergeCell ref="E22:M23"/>
-    <mergeCell ref="A24:D26"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:M24"/>
-    <mergeCell ref="N24:Q26"/>
-    <mergeCell ref="R24:V26"/>
-    <mergeCell ref="E25:M26"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:M15"/>
-    <mergeCell ref="E16:M17"/>
-    <mergeCell ref="N30:Q32"/>
-    <mergeCell ref="R30:V32"/>
-    <mergeCell ref="E31:M32"/>
-    <mergeCell ref="A27:D29"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="N4:V4"/>
-    <mergeCell ref="A5:D9"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:V5"/>
-    <mergeCell ref="E6:V9"/>
-    <mergeCell ref="A18:D20"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:M18"/>
-    <mergeCell ref="N18:Q20"/>
-    <mergeCell ref="A10:D14"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:V10"/>
-    <mergeCell ref="E11:V14"/>
-    <mergeCell ref="N15:Q17"/>
-    <mergeCell ref="A15:D17"/>
-    <mergeCell ref="R18:V20"/>
-    <mergeCell ref="E19:M20"/>
+    <mergeCell ref="A39:D41"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:M39"/>
+    <mergeCell ref="N39:Q41"/>
+    <mergeCell ref="R39:V41"/>
+    <mergeCell ref="E40:M41"/>
+    <mergeCell ref="A42:D44"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:M42"/>
+    <mergeCell ref="N42:Q44"/>
+    <mergeCell ref="R42:V44"/>
+    <mergeCell ref="E43:M44"/>
+    <mergeCell ref="A45:D47"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:M45"/>
+    <mergeCell ref="N45:Q47"/>
+    <mergeCell ref="R45:V47"/>
+    <mergeCell ref="E46:M47"/>
+    <mergeCell ref="A48:D50"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:M48"/>
+    <mergeCell ref="N48:Q50"/>
+    <mergeCell ref="R48:V50"/>
+    <mergeCell ref="E49:M50"/>
+    <mergeCell ref="A51:D53"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:M51"/>
+    <mergeCell ref="N51:Q53"/>
+    <mergeCell ref="R51:V53"/>
+    <mergeCell ref="E52:M53"/>
+    <mergeCell ref="A54:D56"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:M54"/>
+    <mergeCell ref="N54:Q56"/>
+    <mergeCell ref="R54:V56"/>
+    <mergeCell ref="E55:M56"/>
+    <mergeCell ref="A57:D59"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:M57"/>
+    <mergeCell ref="N57:Q59"/>
+    <mergeCell ref="R57:V59"/>
+    <mergeCell ref="E58:M59"/>
+    <mergeCell ref="A60:D62"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:M60"/>
+    <mergeCell ref="N60:Q62"/>
+    <mergeCell ref="R60:V62"/>
+    <mergeCell ref="E61:M62"/>
+    <mergeCell ref="A63:D65"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G63:M63"/>
+    <mergeCell ref="N63:Q65"/>
+    <mergeCell ref="R63:V65"/>
+    <mergeCell ref="E64:M65"/>
+    <mergeCell ref="A66:D68"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="G66:M66"/>
+    <mergeCell ref="N66:Q68"/>
+    <mergeCell ref="R66:V68"/>
+    <mergeCell ref="E67:M68"/>
+    <mergeCell ref="A69:D71"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="G69:M69"/>
+    <mergeCell ref="N69:Q71"/>
+    <mergeCell ref="R69:V71"/>
+    <mergeCell ref="E70:M71"/>
+    <mergeCell ref="A72:D74"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:M72"/>
+    <mergeCell ref="N72:Q74"/>
+    <mergeCell ref="R72:V74"/>
+    <mergeCell ref="E73:M74"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -8196,7 +7108,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8207,7 +7119,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
